--- a/tabtools/qa/output/regtab_ext_test8.xlsx
+++ b/tabtools/qa/output/regtab_ext_test8.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="560" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="616" uniqueCount="26">
   <si>
     <t>Test 8: Mixed Types</t>
   </si>
@@ -97,10 +97,1320 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="3001">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="3301">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -13211,7 +14521,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2311">
+  <borders count="2542">
     <border>
       <left/>
       <right/>
@@ -28909,11 +30219,1580 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2311">
+  <cellXfs count="2542">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -37912,6 +40791,906 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="3000" fillId="0" borderId="2310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2311" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2312" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2313" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2314" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2315" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2316" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2317" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2318" xfId="0"/>
+    <xf numFmtId="0" fontId="3001" fillId="0" borderId="2319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3002" fillId="0" borderId="2320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3003" fillId="0" borderId="2321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3004" fillId="0" borderId="2322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3005" fillId="0" borderId="2323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3006" fillId="0" borderId="2324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3008" fillId="0" borderId="2325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3010" fillId="0" borderId="2326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3012" fillId="0" borderId="2327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3013" fillId="0" borderId="2328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3014" fillId="0" borderId="2329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3015" fillId="0" borderId="2330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3016" fillId="0" borderId="2331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3017" fillId="0" borderId="2332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3018" fillId="0" borderId="2333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3019" fillId="0" borderId="2334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3020" fillId="0" borderId="2335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3021" fillId="0" borderId="2336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3022" fillId="0" borderId="2337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3023" fillId="0" borderId="2338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3024" fillId="0" borderId="2339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3025" fillId="0" borderId="2340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3026" fillId="0" borderId="2341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3027" fillId="0" borderId="2342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3029" fillId="0" borderId="2343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3031" fillId="0" borderId="2344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3033" fillId="0" borderId="2345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3034" fillId="0" borderId="2346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3035" fillId="0" borderId="2347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3036" fillId="0" borderId="2348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3037" fillId="0" borderId="2349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3038" fillId="0" borderId="2350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3039" fillId="0" borderId="2351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3040" fillId="0" borderId="2352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3041" fillId="0" borderId="2353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3042" fillId="0" borderId="2354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3043" fillId="0" borderId="2355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3044" fillId="0" borderId="2356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3045" fillId="0" borderId="2357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3046" fillId="0" borderId="2358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3047" fillId="0" borderId="2359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3048" fillId="0" borderId="2360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3049" fillId="0" borderId="2361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3050" fillId="0" borderId="2362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3051" fillId="0" borderId="2363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3052" fillId="0" borderId="2364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3053" fillId="0" borderId="2365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3054" fillId="0" borderId="2366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3055" fillId="0" borderId="2367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3056" fillId="0" borderId="2368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3057" fillId="0" borderId="2369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3058" fillId="0" borderId="2370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3060" fillId="0" borderId="2371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3062" fillId="0" borderId="2372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3064" fillId="0" borderId="2373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3066" fillId="0" borderId="2374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3068" fillId="0" borderId="2375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3070" fillId="0" borderId="2376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3072" fillId="0" borderId="2377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3074" fillId="0" borderId="2378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3075" fillId="0" borderId="2379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3076" fillId="0" borderId="2380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3077" fillId="0" borderId="2381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3078" fillId="0" borderId="2382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3079" fillId="0" borderId="2383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3080" fillId="0" borderId="2384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3081" fillId="0" borderId="2385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3082" fillId="0" borderId="2386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3083" fillId="0" borderId="2387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3084" fillId="0" borderId="2388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3085" fillId="0" borderId="2389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3086" fillId="0" borderId="2390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3087" fillId="0" borderId="2391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3088" fillId="0" borderId="2392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3089" fillId="0" borderId="2393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3090" fillId="0" borderId="2394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3091" fillId="0" borderId="2395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3092" fillId="0" borderId="2396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3093" fillId="0" borderId="2397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3094" fillId="0" borderId="2398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3095" fillId="0" borderId="2399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3096" fillId="0" borderId="2400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3098" fillId="0" borderId="2401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3100" fillId="0" borderId="2402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3102" fillId="0" borderId="2403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3104" fillId="0" borderId="2404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3106" fillId="0" borderId="2405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3108" fillId="0" borderId="2406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3110" fillId="0" borderId="2407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3111" fillId="0" borderId="2408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3112" fillId="0" borderId="2409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3113" fillId="0" borderId="2410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3114" fillId="0" borderId="2411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3115" fillId="0" borderId="2412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3116" fillId="0" borderId="2413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3117" fillId="0" borderId="2414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3118" fillId="0" borderId="2415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3119" fillId="0" borderId="2416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3120" fillId="0" borderId="2417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3121" fillId="0" borderId="2418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3122" fillId="0" borderId="2419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3123" fillId="0" borderId="2420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3124" fillId="0" borderId="2421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3125" fillId="0" borderId="2422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3126" fillId="0" borderId="2423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3127" fillId="0" borderId="2424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3128" fillId="0" borderId="2425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3129" fillId="0" borderId="2426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3130" fillId="0" borderId="2427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3131" fillId="0" borderId="2428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3132" fillId="0" borderId="2429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3133" fillId="0" borderId="2430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3134" fillId="0" borderId="2431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3135" fillId="0" borderId="2432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3136" fillId="0" borderId="2433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3137" fillId="0" borderId="2434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3138" fillId="0" borderId="2435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3139" fillId="0" borderId="2436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3140" fillId="0" borderId="2437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3141" fillId="0" borderId="2438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3142" fillId="0" borderId="2439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3143" fillId="0" borderId="2440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3144" fillId="0" borderId="2441" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3145" fillId="0" borderId="2442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3146" fillId="0" borderId="2443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3147" fillId="0" borderId="2444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3148" fillId="0" borderId="2445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3149" fillId="0" borderId="2446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3150" fillId="0" borderId="2447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3151" fillId="0" borderId="2448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3152" fillId="0" borderId="2449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3153" fillId="0" borderId="2450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3154" fillId="0" borderId="2451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3155" fillId="0" borderId="2452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3156" fillId="0" borderId="2453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3157" fillId="0" borderId="2454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3158" fillId="0" borderId="2455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3159" fillId="0" borderId="2456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3160" fillId="0" borderId="2457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3161" fillId="0" borderId="2458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3162" fillId="0" borderId="2459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3163" fillId="0" borderId="2460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3164" fillId="0" borderId="2461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3165" fillId="0" borderId="2462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3166" fillId="0" borderId="2463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3167" fillId="0" borderId="2464" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3168" fillId="0" borderId="2465" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3169" fillId="0" borderId="2466" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3170" fillId="0" borderId="2467" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3171" fillId="0" borderId="2468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3172" fillId="0" borderId="2469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3173" fillId="0" borderId="2470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3174" fillId="0" borderId="2471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3175" fillId="0" borderId="2472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3176" fillId="0" borderId="2473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3177" fillId="0" borderId="2474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3178" fillId="0" borderId="2475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3179" fillId="0" borderId="2476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3180" fillId="0" borderId="2477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3181" fillId="0" borderId="2478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3182" fillId="0" borderId="2479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3183" fillId="0" borderId="2480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3184" fillId="0" borderId="2481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3185" fillId="0" borderId="2482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3186" fillId="0" borderId="2483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3187" fillId="0" borderId="2484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3188" fillId="0" borderId="2485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3190" fillId="0" borderId="2486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3192" fillId="0" borderId="2487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3194" fillId="0" borderId="2488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3196" fillId="0" borderId="2489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3198" fillId="0" borderId="2490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3200" fillId="0" borderId="2491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3202" fillId="0" borderId="2492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3204" fillId="0" borderId="2493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3206" fillId="0" borderId="2494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3208" fillId="0" borderId="2495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3210" fillId="0" borderId="2496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3212" fillId="0" borderId="2497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3214" fillId="0" borderId="2498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3216" fillId="0" borderId="2499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3218" fillId="0" borderId="2500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3220" fillId="0" borderId="2501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3222" fillId="0" borderId="2502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3224" fillId="0" borderId="2503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3226" fillId="0" borderId="2504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3228" fillId="0" borderId="2505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3230" fillId="0" borderId="2506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3232" fillId="0" borderId="2507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3234" fillId="0" borderId="2508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3236" fillId="0" borderId="2509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3238" fillId="0" borderId="2510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3240" fillId="0" borderId="2511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3242" fillId="0" borderId="2512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3244" fillId="0" borderId="2513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3246" fillId="0" borderId="2514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3248" fillId="0" borderId="2515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3250" fillId="0" borderId="2516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3252" fillId="0" borderId="2517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3254" fillId="0" borderId="2518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3256" fillId="0" borderId="2519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3258" fillId="0" borderId="2520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3260" fillId="0" borderId="2521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3262" fillId="0" borderId="2522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3264" fillId="0" borderId="2523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3266" fillId="0" borderId="2524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3268" fillId="0" borderId="2525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3270" fillId="0" borderId="2526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3272" fillId="0" borderId="2527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3274" fillId="0" borderId="2528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3276" fillId="0" borderId="2529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3278" fillId="0" borderId="2530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3280" fillId="0" borderId="2531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3282" fillId="0" borderId="2532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3284" fillId="0" borderId="2533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3286" fillId="0" borderId="2534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3288" fillId="0" borderId="2535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3290" fillId="0" borderId="2536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3292" fillId="0" borderId="2537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3294" fillId="0" borderId="2538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3296" fillId="0" borderId="2539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3298" fillId="0" borderId="2540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3300" fillId="0" borderId="2541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -37927,194 +41706,194 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" style="2081" customWidth="true"/>
-    <col min="3" max="3" width="5.3203125" style="2082" customWidth="true"/>
-    <col min="6" max="6" width="5.3203125" style="2083" customWidth="true"/>
-    <col min="4" max="4" width="11.6015625" style="2084" customWidth="true"/>
-    <col min="7" max="7" width="11.6015625" style="2085" customWidth="true"/>
-    <col min="5" max="5" width="8.0390625" style="2086" customWidth="true"/>
-    <col min="8" max="8" width="8.0390625" style="2087" customWidth="true"/>
+    <col min="2" max="2" width="14.7109375" style="2312" customWidth="true"/>
+    <col min="3" max="3" width="5.3203125" style="2313" customWidth="true"/>
+    <col min="6" max="6" width="5.3203125" style="2314" customWidth="true"/>
+    <col min="4" max="4" width="11.6015625" style="2315" customWidth="true"/>
+    <col min="7" max="7" width="11.6015625" style="2316" customWidth="true"/>
+    <col min="5" max="5" width="8.0390625" style="2317" customWidth="true"/>
+    <col min="8" max="8" width="8.0390625" style="2318" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="2080" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="2255" t="s">
+    <row r="1" s="2311" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="2486" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2256" t="s">
+      <c r="B1" s="2487" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2257" t="s">
+      <c r="C1" s="2488" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2258" t="s">
+      <c r="D1" s="2489" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2259" t="s">
+      <c r="E1" s="2490" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2260" t="s">
+      <c r="F1" s="2491" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="2261" t="s">
+      <c r="G1" s="2492" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="2262" t="s">
+      <c r="H1" s="2493" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2263" t="s">
+      <c r="A2" s="2494" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2264" t="s">
+      <c r="B2" s="2495" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2265" t="s">
+      <c r="C2" s="2496" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2266" t="s">
+      <c r="D2" s="2497" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2267" t="s">
+      <c r="E2" s="2498" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="2268" t="s">
+      <c r="F2" s="2499" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2269" t="s">
+      <c r="G2" s="2500" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="2270" t="s">
+      <c r="H2" s="2501" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2271" t="s">
+      <c r="A3" s="2502" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2272" t="s">
+      <c r="B3" s="2503" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2273" t="s">
+      <c r="C3" s="2504" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2274" t="s">
+      <c r="D3" s="2505" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2275" t="s">
+      <c r="E3" s="2506" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2276" t="s">
+      <c r="F3" s="2507" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="2277" t="s">
+      <c r="G3" s="2508" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="2278" t="s">
+      <c r="H3" s="2509" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2279" t="s">
+      <c r="A4" s="2510" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2280" t="s">
+      <c r="B4" s="2511" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="2281" t="s">
+      <c r="C4" s="2512" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2282" t="s">
+      <c r="D4" s="2513" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="2283" t="s">
+      <c r="E4" s="2514" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="2284" t="s">
+      <c r="F4" s="2515" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="2285" t="s">
+      <c r="G4" s="2516" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="2286" t="s">
+      <c r="H4" s="2517" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2287" t="s">
+      <c r="A5" s="2518" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="2288" t="s">
+      <c r="B5" s="2519" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2289" t="s">
+      <c r="C5" s="2520" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="2290" t="s">
+      <c r="D5" s="2521" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="2291" t="s">
+      <c r="E5" s="2522" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="2292" t="s">
+      <c r="F5" s="2523" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="2293" t="s">
+      <c r="G5" s="2524" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="2294" t="s">
+      <c r="H5" s="2525" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2295" t="s">
+      <c r="A6" s="2526" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="2296" t="s">
+      <c r="B6" s="2527" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="2297" t="s">
+      <c r="C6" s="2528" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="2298" t="s">
+      <c r="D6" s="2529" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="2299" t="s">
+      <c r="E6" s="2530" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="2300" t="s">
+      <c r="F6" s="2531" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="2301" t="s">
+      <c r="G6" s="2532" t="s">
         <v>1</v>
       </c>
-      <c r="H6" s="2302" t="s">
+      <c r="H6" s="2533" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2303" t="s">
+      <c r="A7" s="2534" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="2304" t="s">
+      <c r="B7" s="2535" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="2305" t="s">
+      <c r="C7" s="2536" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="2306" t="s">
+      <c r="D7" s="2537" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="2307" t="s">
+      <c r="E7" s="2538" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="2308" t="s">
+      <c r="F7" s="2539" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="2309" t="s">
+      <c r="G7" s="2540" t="s">
         <v>1</v>
       </c>
-      <c r="H7" s="2310" t="s">
+      <c r="H7" s="2541" t="s">
         <v>1</v>
       </c>
     </row>
